--- a/Config/Excel/language/lang_monster.xlsx
+++ b/Config/Excel/language/lang_monster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20379"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProjects\Project001\Config\Excel\language\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\Project001\Config\Excel\language\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAFCE219-FD25-4B17-B98F-1866F86ECF16}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D93444C-81A8-4D9E-98FF-928B8EF91E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="11655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lang_system" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>id</t>
   </si>
@@ -30,13 +30,7 @@
     <t>text</t>
   </si>
   <si>
-    <t>color</t>
-  </si>
-  <si>
     <t>c</t>
-  </si>
-  <si>
-    <t>int</t>
   </si>
   <si>
     <t>string</t>
@@ -451,110 +445,83 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.625" customWidth="1"/>
-    <col min="2" max="2" width="37.25" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="2" max="2" width="37.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" t="s">
         <v>9</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -567,30 +534,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>91</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>93</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -603,7 +570,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
